--- a/BasicPerformer/Implementation/Data/Config.xlsx
+++ b/BasicPerformer/Implementation/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eyash\OneDrive\Documents\UiPath\LazyFramework.DX.Shared\Frameworks\Performers\BasicPerformer\Implementation\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.brahmbhatt\Documents\UiPath\LazyFramework.DX.Shared\BasicPerformer\Implementation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AAD066-AB06-47E8-AB51-76D8C822073B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC0F24-5DC5-4868-9370-65951E39ABB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="20670" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="4365" windowWidth="20205" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t>Name</t>
   </si>
@@ -66,18 +66,6 @@
     <t>The folder of the queue to add items to.</t>
   </si>
   <si>
-    <t>CredentialName_Email</t>
-  </si>
-  <si>
-    <t>CredentialFolder_Email</t>
-  </si>
-  <si>
-    <t>The name of the credential used to send emails from the SMTP server.</t>
-  </si>
-  <si>
-    <t>The folder of the credentuals used to send emails from the SMTP server.</t>
-  </si>
-  <si>
     <t>Folder_ExScreenshots</t>
   </si>
   <si>
@@ -180,9 +168,6 @@
     <t>LazyFramework</t>
   </si>
   <si>
-    <t>Credentials_Email</t>
-  </si>
-  <si>
     <t>Maintenance_Start</t>
   </si>
   <si>
@@ -198,31 +183,31 @@
     <t>The start of a maintenance window.</t>
   </si>
   <si>
-    <t>Design\Modules\Performers\Basic\Data\Exception Screenshots</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
     <t>Text</t>
   </si>
   <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\SysEx_Subject.txt</t>
-  </si>
-  <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\SysEx_Body.html</t>
-  </si>
-  <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\TransSysEx_Subject.txt</t>
-  </si>
-  <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\TransSysEx_Body.html</t>
-  </si>
-  <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\TransBusEx_Subject.txt</t>
-  </si>
-  <si>
-    <t>Frameworks\Performers\BasicPerformer\Implementation\Data\Templates\TransBusEx_Body.html</t>
+    <t>BasicPerformer\Implementation\Data\Templates\SysEx_Subject.txt</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Templates\SysEx_Body.html</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Templates\TransSysEx_Subject.txt</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Templates\TransSysEx_Body.html</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Templates\TransBusEx_Subject.txt</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Templates\TransBusEx_Body.html</t>
+  </si>
+  <si>
+    <t>BasicPerformer\Implementation\Data\Exception Screenshots</t>
   </si>
 </sst>
 </file>
@@ -541,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -565,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -576,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -587,7 +572,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -598,62 +583,40 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>47</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -684,24 +647,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -734,86 +697,86 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -857,86 +820,86 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
         <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
